--- a/example/GOOGL_Demo_Integrated_Financials.xlsx
+++ b/example/GOOGL_Demo_Integrated_Financials.xlsx
@@ -7418,7 +7418,7 @@
     <row r="83">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>PROFESSOR'S STRATEGIC NOTES — BULL</t>
+          <t>SCENARIO RATIONALE — BULL</t>
         </is>
       </c>
       <c r="B83" s="99" t="n"/>
@@ -32940,7 +32940,7 @@
     <row r="83">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>PROFESSOR'S STRATEGIC NOTES — BEAR</t>
+          <t>SCENARIO RATIONALE — BEAR</t>
         </is>
       </c>
       <c r="B83" s="99" t="n"/>
@@ -36354,7 +36354,7 @@
     <row r="83">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>PROFESSOR'S STRATEGIC NOTES — BASE</t>
+          <t>SCENARIO RATIONALE — BASE</t>
         </is>
       </c>
       <c r="B83" s="99" t="n"/>

--- a/example/GOOGL_Demo_Integrated_Financials.xlsx
+++ b/example/GOOGL_Demo_Integrated_Financials.xlsx
@@ -789,7 +789,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEMO WORKBOOK: financial data as filed with the SEC (real); model inputs ILLUSTRATIVE ONLY — not analysis, not advice.</t>
+          <t>DEMO WORKBOOK: as-filed SEC financials (real) + the analyst's actual GOOGL model assumptions; scenario reasoning withheld. Illustrates the system; not investment advice.</t>
         </is>
       </c>
     </row>
@@ -4603,34 +4603,34 @@
         <v/>
       </c>
       <c r="L11" s="29" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M11" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N11" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O11" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P11" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="M11" s="29" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="N11" s="29" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O11" s="29" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="P11" s="29" t="n">
+      <c r="Q11" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R11" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T11" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q11" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="R11" s="29" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S11" s="29" t="n">
+      <c r="U11" s="29" t="n">
         <v>0.06</v>
-      </c>
-      <c r="T11" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="U11" s="29" t="n">
-        <v>0.04</v>
       </c>
       <c r="W11" s="1">
         <f>AVERAGE(C11:K11)</f>
@@ -4684,34 +4684,34 @@
         <v/>
       </c>
       <c r="L12" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M12" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N12" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O12" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P12" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q12" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R12" s="29" t="n">
         <v>0.32</v>
       </c>
-      <c r="M12" s="29" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="N12" s="29" t="n">
+      <c r="S12" s="29" t="n">
         <v>0.31</v>
       </c>
-      <c r="O12" s="29" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="P12" s="29" t="n">
+      <c r="T12" s="29" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U12" s="29" t="n">
         <v>0.3</v>
-      </c>
-      <c r="Q12" s="29" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="R12" s="29" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="S12" s="29" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="T12" s="29" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U12" s="29" t="n">
-        <v>0.28</v>
       </c>
       <c r="W12" s="1">
         <f>AVERAGE(C12:K12)</f>
@@ -4766,35 +4766,36 @@
         <f>K21/K31</f>
         <v/>
       </c>
-      <c r="L14" s="30" t="n">
-        <v>0.02</v>
+      <c r="L14" s="30">
+        <f>L21/L31</f>
+        <v/>
       </c>
       <c r="M14" s="31" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="R14" s="31" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="S14" s="31" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="T14" s="31" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="U14" s="31" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="W14" s="2">
         <f>AVERAGE(C14:K14)</f>
@@ -4848,35 +4849,36 @@
         <f>K22/K31</f>
         <v/>
       </c>
-      <c r="L15" s="30" t="n">
-        <v>0.5</v>
+      <c r="L15" s="30">
+        <f>L22/L31</f>
+        <v/>
       </c>
       <c r="M15" s="31" t="n">
-        <v>0.55</v>
+        <v>0.9821</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>0.6</v>
+        <v>1.0321</v>
       </c>
       <c r="O15" s="31" t="n">
-        <v>0.65</v>
+        <v>1.0821</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>0.7</v>
+        <v>1.1221</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>0.75</v>
+        <v>1.1621</v>
       </c>
       <c r="R15" s="31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S15" s="31" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="T15" s="31" t="n">
         <v>0.9</v>
       </c>
       <c r="U15" s="31" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W15" s="2">
         <f>AVERAGE(C15:K15)</f>
@@ -7445,7 +7447,7 @@
     <row r="84">
       <c r="A84" s="99" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE BULL — generic durable-growth inputs for demonstration. Not analysis.</t>
+          <t>Scenario reasoning is withheld from the public demo. The blue model inputs above are the actual GOOGL coverage assumptions; the written rationale behind them is kept private. Not investment advice.</t>
         </is>
       </c>
       <c r="B84" s="99" t="n"/>
@@ -7796,7 +7798,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Probability-Weighted Residual Income Valuation — ILLUSTRATIVE inputs (see model tabs); not analysis</t>
+          <t>Probability-Weighted Residual Income Valuation — GOOGL coverage build (as-analyzed inputs; scenario reasoning withheld). Not investment advice.</t>
         </is>
       </c>
     </row>
@@ -7835,13 +7837,13 @@
         </is>
       </c>
       <c r="B5" s="33" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="C5" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="D5" s="33" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6"/>
@@ -9020,7 +9022,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Live ICC: the discount rate at which each scenario's IVPS equals the price in B5. Reactive — recomputes when the price or any model input changes. Model inputs ILLUSTRATIVE; not analysis.</t>
+          <t>Live ICC: the discount rate at which each scenario's IVPS equals the price in B5. Reactive — recomputes when the price or any model input changes. GOOGL coverage build; not investment advice.</t>
         </is>
       </c>
     </row>
@@ -30125,34 +30127,34 @@
         <v/>
       </c>
       <c r="L11" s="29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M11" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N11" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O11" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P11" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q11" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" s="29" t="n">
+      <c r="R11" s="29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S11" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="N11" s="29" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O11" s="29" t="n">
+      <c r="T11" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="P11" s="29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q11" s="29" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R11" s="29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T11" s="29" t="n">
-        <v>0.03</v>
-      </c>
       <c r="U11" s="29" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="W11" s="1">
         <f>AVERAGE(C11:K11)</f>
@@ -30206,34 +30208,34 @@
         <v/>
       </c>
       <c r="L12" s="29" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="M12" s="29" t="n">
-        <v>0.235</v>
+        <v>0.31</v>
       </c>
       <c r="N12" s="29" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="O12" s="29" t="n">
-        <v>0.225</v>
+        <v>0.3</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>0.215</v>
+        <v>0.29</v>
       </c>
       <c r="R12" s="29" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>0.205</v>
+        <v>0.28</v>
       </c>
       <c r="T12" s="29" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="U12" s="29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="W12" s="1">
         <f>AVERAGE(C12:K12)</f>
@@ -30288,35 +30290,36 @@
         <f>K21/K31</f>
         <v/>
       </c>
-      <c r="L14" s="30" t="n">
-        <v>0.02</v>
+      <c r="L14" s="30">
+        <f>L21/L31</f>
+        <v/>
       </c>
       <c r="M14" s="31" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="R14" s="31" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="S14" s="31" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="T14" s="31" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="U14" s="31" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="W14" s="2">
         <f>AVERAGE(C14:K14)</f>
@@ -30370,35 +30373,36 @@
         <f>K22/K31</f>
         <v/>
       </c>
-      <c r="L15" s="30" t="n">
-        <v>0.5</v>
+      <c r="L15" s="30">
+        <f>L22/L31</f>
+        <v/>
       </c>
       <c r="M15" s="31" t="n">
-        <v>0.55</v>
+        <v>1.0221</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>0.6</v>
+        <v>1.1221</v>
       </c>
       <c r="O15" s="31" t="n">
-        <v>0.65</v>
+        <v>1.2021</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>0.7</v>
+        <v>1.2821</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>0.75</v>
+        <v>1.3521</v>
       </c>
       <c r="R15" s="31" t="n">
-        <v>0.8</v>
+        <v>1.4121</v>
       </c>
       <c r="S15" s="31" t="n">
-        <v>0.85</v>
+        <v>1.4621</v>
       </c>
       <c r="T15" s="31" t="n">
-        <v>0.9</v>
+        <v>1.5121</v>
       </c>
       <c r="U15" s="31" t="n">
-        <v>0.95</v>
+        <v>1.5521</v>
       </c>
       <c r="W15" s="2">
         <f>AVERAGE(C15:K15)</f>
@@ -32967,7 +32971,7 @@
     <row r="84">
       <c r="A84" s="99" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE BEAR — generic deceleration-and-compression inputs for demonstration. Not analysis. Run /bav-pipeline to build scenarios from an actual strategy report.</t>
+          <t>Scenario reasoning is withheld from the public demo. The blue model inputs above are the actual GOOGL coverage assumptions; the written rationale behind them is kept private. Not investment advice.</t>
         </is>
       </c>
       <c r="B84" s="99" t="n"/>
@@ -33322,7 +33326,7 @@
         </is>
       </c>
       <c r="B2" s="26" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="3">
@@ -33539,34 +33543,34 @@
         <v/>
       </c>
       <c r="L11" s="29" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="M11" s="29" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="N11" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O11" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P11" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q11" s="29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R11" s="29" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T11" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="O11" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="P11" s="29" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q11" s="29" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R11" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S11" s="29" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="T11" s="29" t="n">
+      <c r="U11" s="29" t="n">
         <v>0.04</v>
-      </c>
-      <c r="U11" s="29" t="n">
-        <v>0.035</v>
       </c>
       <c r="W11" s="1">
         <f>AVERAGE(C11:K11)</f>
@@ -33620,34 +33624,34 @@
         <v/>
       </c>
       <c r="L12" s="29" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="M12" s="29" t="n">
-        <v>0.275</v>
+        <v>0.32</v>
       </c>
       <c r="N12" s="29" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="O12" s="29" t="n">
-        <v>0.265</v>
+        <v>0.32</v>
       </c>
       <c r="P12" s="29" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>0.255</v>
+        <v>0.32</v>
       </c>
       <c r="R12" s="29" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>0.245</v>
+        <v>0.31</v>
       </c>
       <c r="T12" s="29" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="U12" s="29" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="W12" s="1">
         <f>AVERAGE(C12:K12)</f>
@@ -33702,35 +33706,36 @@
         <f>K21/K31</f>
         <v/>
       </c>
-      <c r="L14" s="30" t="n">
-        <v>0.02</v>
+      <c r="L14" s="30">
+        <f>L21/L31</f>
+        <v/>
       </c>
       <c r="M14" s="31" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O14" s="31" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="P14" s="31" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="31" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="R14" s="31" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="S14" s="31" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="T14" s="31" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="U14" s="31" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="W14" s="2">
         <f>AVERAGE(C14:K14)</f>
@@ -33784,35 +33789,36 @@
         <f>K22/K31</f>
         <v/>
       </c>
-      <c r="L15" s="30" t="n">
-        <v>0.5</v>
+      <c r="L15" s="30">
+        <f>L22/L31</f>
+        <v/>
       </c>
       <c r="M15" s="31" t="n">
-        <v>0.55</v>
+        <v>0.9821</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>0.6</v>
+        <v>1.0321</v>
       </c>
       <c r="O15" s="31" t="n">
-        <v>0.65</v>
+        <v>1.0821</v>
       </c>
       <c r="P15" s="31" t="n">
-        <v>0.7</v>
+        <v>1.1221</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>0.75</v>
+        <v>1.1621</v>
       </c>
       <c r="R15" s="31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S15" s="31" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="T15" s="31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U15" s="31" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="W15" s="2">
         <f>AVERAGE(C15:K15)</f>
@@ -36381,7 +36387,7 @@
     <row r="84">
       <c r="A84" s="99" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE BASE — generic moderate-fade inputs for demonstration. Not analysis.</t>
+          <t>Scenario reasoning is withheld from the public demo. The blue model inputs above are the actual GOOGL coverage assumptions; the written rationale behind them is kept private. Not investment advice.</t>
         </is>
       </c>
       <c r="B84" s="99" t="n"/>

--- a/example/GOOGL_Demo_Integrated_Financials.xlsx
+++ b/example/GOOGL_Demo_Integrated_Financials.xlsx
@@ -789,7 +789,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEMO WORKBOOK: as-filed SEC financials (real) + the analyst's actual GOOGL model assumptions; scenario reasoning withheld. Illustrates the system; not investment advice.</t>
+          <t>DEMO WORKBOOK — deliberately illustrative: a complete, real GOOGL coverage build (as-filed SEC financials + the analyst's actual model assumptions and reasoning) shown to demonstrate the system. Not investment advice.</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
     <row r="83">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>SCENARIO RATIONALE — BULL</t>
+          <t>SCENARIO RATIONALE — BULL CASE</t>
         </is>
       </c>
       <c r="B83" s="99" t="n"/>
@@ -7445,11 +7445,7 @@
       <c r="U83" s="99" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="99" t="inlineStr">
-        <is>
-          <t>Scenario reasoning is withheld from the public demo. The blue model inputs above are the actual GOOGL coverage assumptions; the written rationale behind them is kept private. Not investment advice.</t>
-        </is>
-      </c>
+      <c r="A84" s="99" t="n"/>
       <c r="B84" s="99" t="n"/>
       <c r="C84" s="99" t="n"/>
       <c r="D84" s="99" t="n"/>
@@ -7472,7 +7468,11 @@
       <c r="U84" s="99" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="76" t="n"/>
+      <c r="A85" s="76" t="inlineStr">
+        <is>
+          <t>Growth Assumption Rationale:</t>
+        </is>
+      </c>
       <c r="B85" s="99" t="n"/>
       <c r="C85" s="99" t="n"/>
       <c r="D85" s="99" t="n"/>
@@ -7495,6 +7495,11 @@
       <c r="U85" s="99" t="n"/>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI supercharges Search monetization (higher RPQ, new ad formats). Cloud accelerates to become #2 behind AWS at 30%+ margins. Gemini ecosystem drives new revenue streams. Waymo begins meaningful revenue contribution.</t>
+        </is>
+      </c>
       <c r="B86" s="99" t="n"/>
       <c r="C86" s="99" t="n"/>
       <c r="D86" s="99" t="n"/>
@@ -7540,7 +7545,11 @@
       <c r="U87" s="99" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="76" t="n"/>
+      <c r="A88" s="76" t="inlineStr">
+        <is>
+          <t>Margin &amp; Moat Assessment:</t>
+        </is>
+      </c>
       <c r="B88" s="99" t="n"/>
       <c r="C88" s="99" t="n"/>
       <c r="D88" s="99" t="n"/>
@@ -7563,6 +7572,11 @@
       <c r="U88" s="99" t="n"/>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full-stack AI moat proves durable. Operating margins expand near-term as Cloud reaches scale economies. CapEx investments generate strong ROIC through proprietary TPU advantages and data flywheel effects.</t>
+        </is>
+      </c>
       <c r="B89" s="99" t="n"/>
       <c r="C89" s="99" t="n"/>
       <c r="D89" s="99" t="n"/>
@@ -7608,7 +7622,11 @@
       <c r="U90" s="99" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="76" t="n"/>
+      <c r="A91" s="76" t="inlineStr">
+        <is>
+          <t>Key Risks to Monitor:</t>
+        </is>
+      </c>
       <c r="B91" s="99" t="n"/>
       <c r="C91" s="99" t="n"/>
       <c r="D91" s="99" t="n"/>
@@ -7631,6 +7649,11 @@
       <c r="U91" s="99" t="n"/>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Antitrust outcome more benign than feared. AI investment cycle pays off faster than expected. Risk of overpaying for growth if AI hype deflates.</t>
+        </is>
+      </c>
       <c r="B92" s="99" t="n"/>
       <c r="C92" s="99" t="n"/>
       <c r="D92" s="99" t="n"/>
@@ -7676,7 +7699,11 @@
       <c r="U93" s="99" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="76" t="n"/>
+      <c r="A94" s="76" t="inlineStr">
+        <is>
+          <t>Valuation Context:</t>
+        </is>
+      </c>
       <c r="B94" s="99" t="n"/>
       <c r="C94" s="99" t="n"/>
       <c r="D94" s="99" t="n"/>
@@ -7699,6 +7726,11 @@
       <c r="U94" s="99" t="n"/>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Bull case reflects Alphabet as the preeminent AI platform company, successfully monetizing its unique vertical integration across hardware, models, applications, and distribution.</t>
+        </is>
+      </c>
       <c r="B95" s="99" t="n"/>
       <c r="C95" s="99" t="n"/>
       <c r="D95" s="99" t="n"/>
@@ -7798,7 +7830,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Probability-Weighted Residual Income Valuation — GOOGL coverage build (as-analyzed inputs; scenario reasoning withheld). Not investment advice.</t>
+          <t>Probability-Weighted Residual Income Valuation — deliberately illustrative demo (a real GOOGL coverage build). Not investment advice.</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9054,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Live ICC: the discount rate at which each scenario's IVPS equals the price in B5. Reactive — recomputes when the price or any model input changes. GOOGL coverage build; not investment advice.</t>
+          <t>Live ICC: the discount rate at which each scenario's IVPS equals the price in B5. Reactive — recomputes when the price or any model input changes. Deliberately illustrative demo; not investment advice.</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32976,7 @@
     <row r="83">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>SCENARIO RATIONALE — BEAR</t>
+          <t>SCENARIO RATIONALE — BEAR CASE</t>
         </is>
       </c>
       <c r="B83" s="99" t="n"/>
@@ -32969,11 +33001,7 @@
       <c r="U83" s="99" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="99" t="inlineStr">
-        <is>
-          <t>Scenario reasoning is withheld from the public demo. The blue model inputs above are the actual GOOGL coverage assumptions; the written rationale behind them is kept private. Not investment advice.</t>
-        </is>
-      </c>
+      <c r="A84" s="99" t="n"/>
       <c r="B84" s="99" t="n"/>
       <c r="C84" s="99" t="n"/>
       <c r="D84" s="99" t="n"/>
@@ -32996,7 +33024,11 @@
       <c r="U84" s="99" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="76" t="n"/>
+      <c r="A85" s="76" t="inlineStr">
+        <is>
+          <t>Growth Assumption Rationale:</t>
+        </is>
+      </c>
       <c r="B85" s="99" t="n"/>
       <c r="C85" s="99" t="n"/>
       <c r="D85" s="99" t="n"/>
@@ -33019,6 +33051,11 @@
       <c r="U85" s="99" t="n"/>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI disrupts Search ad monetization; Cloud growth decelerates to &lt;20% as pricing pressure from AWS/Azure intensifies. Antitrust remedies (Chrome/AdX divestiture) structurally weaken ecosystem. Revenue growth trends toward GDP+inflation.</t>
+        </is>
+      </c>
       <c r="B86" s="99" t="n"/>
       <c r="C86" s="99" t="n"/>
       <c r="D86" s="99" t="n"/>
@@ -33064,7 +33101,11 @@
       <c r="U87" s="99" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="76" t="n"/>
+      <c r="A88" s="76" t="inlineStr">
+        <is>
+          <t>Margin &amp; Moat Assessment:</t>
+        </is>
+      </c>
       <c r="B88" s="99" t="n"/>
       <c r="C88" s="99" t="n"/>
       <c r="D88" s="99" t="n"/>
@@ -33087,6 +33128,11 @@
       <c r="U88" s="99" t="n"/>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Search share erodes to ~75% as AI alternatives gain traction. Cloud margins plateau at ~20%. Operating margin compresses toward 25% as massive CapEx ($175B+) fails to generate proportional returns.</t>
+        </is>
+      </c>
       <c r="B89" s="99" t="n"/>
       <c r="C89" s="99" t="n"/>
       <c r="D89" s="99" t="n"/>
@@ -33132,7 +33178,11 @@
       <c r="U90" s="99" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="76" t="n"/>
+      <c r="A91" s="76" t="inlineStr">
+        <is>
+          <t>Key Risks to Monitor:</t>
+        </is>
+      </c>
       <c r="B91" s="99" t="n"/>
       <c r="C91" s="99" t="n"/>
       <c r="D91" s="99" t="n"/>
@@ -33155,6 +33205,11 @@
       <c r="U91" s="99" t="n"/>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DOJ structural breakup, AI cannibalization of Search revenue, CapEx overcapacity, geopolitical chip supply disruption, regulatory fines accumulating globally.</t>
+        </is>
+      </c>
       <c r="B92" s="99" t="n"/>
       <c r="C92" s="99" t="n"/>
       <c r="D92" s="99" t="n"/>
@@ -33200,7 +33255,11 @@
       <c r="U93" s="99" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="76" t="n"/>
+      <c r="A94" s="76" t="inlineStr">
+        <is>
+          <t>Valuation Context:</t>
+        </is>
+      </c>
       <c r="B94" s="99" t="n"/>
       <c r="C94" s="99" t="n"/>
       <c r="D94" s="99" t="n"/>
@@ -33223,6 +33282,11 @@
       <c r="U94" s="99" t="n"/>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Bear case reflects a world where Alphabet becomes a regulated utility-like company with deteriorating competitive position and massive capital requirements.</t>
+        </is>
+      </c>
       <c r="B95" s="99" t="n"/>
       <c r="C95" s="99" t="n"/>
       <c r="D95" s="99" t="n"/>
@@ -33245,7 +33309,11 @@
       <c r="U95" s="99" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="74" t="n"/>
+      <c r="A96" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Company becomes way more capital intensive, and under intense competition, margins erode and sales growth from investments not as significant. </t>
+        </is>
+      </c>
       <c r="B96" s="99" t="n"/>
       <c r="C96" s="99" t="n"/>
       <c r="D96" s="99" t="n"/>
@@ -36360,7 +36428,7 @@
     <row r="83">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>SCENARIO RATIONALE — BASE</t>
+          <t>SCENARIO RATIONALE — BASE CASE</t>
         </is>
       </c>
       <c r="B83" s="99" t="n"/>
@@ -36385,11 +36453,7 @@
       <c r="U83" s="99" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="99" t="inlineStr">
-        <is>
-          <t>Scenario reasoning is withheld from the public demo. The blue model inputs above are the actual GOOGL coverage assumptions; the written rationale behind them is kept private. Not investment advice.</t>
-        </is>
-      </c>
+      <c r="A84" s="99" t="n"/>
       <c r="B84" s="99" t="n"/>
       <c r="C84" s="99" t="n"/>
       <c r="D84" s="99" t="n"/>
@@ -36412,7 +36476,11 @@
       <c r="U84" s="99" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="76" t="n"/>
+      <c r="A85" s="76" t="inlineStr">
+        <is>
+          <t>Growth Assumption Rationale:</t>
+        </is>
+      </c>
       <c r="B85" s="99" t="n"/>
       <c r="C85" s="99" t="n"/>
       <c r="D85" s="99" t="n"/>
@@ -36435,6 +36503,11 @@
       <c r="U85" s="99" t="n"/>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Search maintains dominance with AI Overviews enhancing engagement. Cloud sustains 20-25% growth through AI Vertex platform. YouTube crosses $60B+ annually. Revenue growth gradually decelerates as base expands past $500B.</t>
+        </is>
+      </c>
       <c r="B86" s="99" t="n"/>
       <c r="C86" s="99" t="n"/>
       <c r="D86" s="99" t="n"/>
@@ -36480,7 +36553,11 @@
       <c r="U87" s="99" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="76" t="n"/>
+      <c r="A88" s="76" t="inlineStr">
+        <is>
+          <t>Margin &amp; Moat Assessment:</t>
+        </is>
+      </c>
       <c r="B88" s="99" t="n"/>
       <c r="C88" s="99" t="n"/>
       <c r="D88" s="99" t="n"/>
@@ -36503,6 +36580,11 @@
       <c r="U88" s="99" t="n"/>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full-stack advantage (Gemini + TPUs + Android/Chrome + Search data) provides durable moat. Operating margins stabilize ~27% near-term then compress modestly as CapEx normalizes. Antitrust results in behavioral remedies, not structural breakup.</t>
+        </is>
+      </c>
       <c r="B89" s="99" t="n"/>
       <c r="C89" s="99" t="n"/>
       <c r="D89" s="99" t="n"/>
@@ -36548,7 +36630,11 @@
       <c r="U90" s="99" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="76" t="n"/>
+      <c r="A91" s="76" t="inlineStr">
+        <is>
+          <t>Key Risks to Monitor:</t>
+        </is>
+      </c>
       <c r="B91" s="99" t="n"/>
       <c r="C91" s="99" t="n"/>
       <c r="D91" s="99" t="n"/>
@@ -36571,6 +36657,11 @@
       <c r="U91" s="99" t="n"/>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AI competition from OpenAI/Meta intensifies, margin pressure from $175B+ annual CapEx, some Search cannibalization offset by Cloud growth, moderate regulatory drag.</t>
+        </is>
+      </c>
       <c r="B92" s="99" t="n"/>
       <c r="C92" s="99" t="n"/>
       <c r="D92" s="99" t="n"/>
@@ -36616,7 +36707,11 @@
       <c r="U93" s="99" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="76" t="n"/>
+      <c r="A94" s="76" t="inlineStr">
+        <is>
+          <t>Valuation Context:</t>
+        </is>
+      </c>
       <c r="B94" s="99" t="n"/>
       <c r="C94" s="99" t="n"/>
       <c r="D94" s="99" t="n"/>
@@ -36639,6 +36734,11 @@
       <c r="U94" s="99" t="n"/>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Base case reflects Alphabet as a dominant but maturing tech platform that successfully navigates the AI transition while returning capital aggressively through buybacks and dividends.</t>
+        </is>
+      </c>
       <c r="B95" s="99" t="n"/>
       <c r="C95" s="99" t="n"/>
       <c r="D95" s="99" t="n"/>
@@ -36661,7 +36761,11 @@
       <c r="U95" s="99" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="74" t="n"/>
+      <c r="A96" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Company bcomes more capital intensive, bringing down RNOA, but ultimately drives search (revenues) and increases margins. </t>
+        </is>
+      </c>
       <c r="B96" s="99" t="n"/>
       <c r="C96" s="99" t="n"/>
       <c r="D96" s="99" t="n"/>
